--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_21_5.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_21_5.xlsx
@@ -517,52 +517,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9994391329224747</v>
+        <v>0.9993524871884956</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6737279036870318</v>
+        <v>0.7094587854171508</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9990728608136972</v>
+        <v>0.9997539683592864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999803634708215</v>
+        <v>0.99927879439169</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9996957835147632</v>
+        <v>0.9994860959155901</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003329549254152689</v>
+        <v>0.0003843915760060278</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1936892105920642</v>
+        <v>0.1724778157033432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005744650018565919</v>
+        <v>8.522565495961704e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002303817522823258</v>
+        <v>0.0004819411798621255</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004024228000157206</v>
+        <v>0.0002835834174108713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01010288146743945</v>
+        <v>0.01173089864817813</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01824705251308465</v>
+        <v>0.0196059066611577</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000384594567446</v>
+        <v>1.000444008785032</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0190238673151726</v>
+        <v>0.02044057069754498</v>
       </c>
       <c r="P2" t="n">
-        <v>134.015006872518</v>
+        <v>133.7276975915296</v>
       </c>
       <c r="Q2" t="n">
-        <v>205.9286805397419</v>
+        <v>205.6413712587534</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +572,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.999440290042831</v>
+        <v>0.9994682678298111</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6727685716833232</v>
+        <v>0.709044328459691</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9987957547691314</v>
+        <v>0.9996688322884072</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9997463989787285</v>
+        <v>0.9994261560649617</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9996055028542519</v>
+        <v>0.9995486000635057</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003322680087867708</v>
+        <v>0.0003156591858578351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1942587115104504</v>
+        <v>0.1727238552568998</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000746162764994743</v>
+        <v>0.0001147168918603853</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002975324566272568</v>
+        <v>0.0003834676546084761</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005218476108109998</v>
+        <v>0.0002490922732344307</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0105444210858148</v>
+        <v>0.01073938273555011</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01822822012119589</v>
+        <v>0.01776680010181448</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000383801113487</v>
+        <v>1.000364616345272</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01900423318937271</v>
+        <v>0.01852316956449512</v>
       </c>
       <c r="P3" t="n">
-        <v>134.0191373186427</v>
+        <v>134.1216949043423</v>
       </c>
       <c r="Q3" t="n">
-        <v>205.9328109858665</v>
+        <v>206.0353685715661</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9994297207364694</v>
+        <v>0.999557294509781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6718245021665997</v>
+        <v>0.7085319407969817</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9985184319179187</v>
+        <v>0.9995706814327983</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9996917005349577</v>
+        <v>0.9995387564169954</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9995162970359383</v>
+        <v>0.9995859702965733</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003385424056131995</v>
+        <v>0.000262809102875392</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1948191519572571</v>
+        <v>0.1730280307074785</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000917994863767408</v>
+        <v>0.0001487164657763666</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003617063399469247</v>
+        <v>0.0003082231669245157</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006398506018571663</v>
+        <v>0.0002284705682815713</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01091278175448582</v>
+        <v>0.00984911728879528</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01839952188545125</v>
+        <v>0.01621138806134107</v>
       </c>
       <c r="N4" t="n">
-        <v>1.00039104863785</v>
+        <v>1.000303569479007</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01918282762437595</v>
+        <v>0.01690154041331196</v>
       </c>
       <c r="P4" t="n">
-        <v>133.9817223967646</v>
+        <v>134.488165267839</v>
       </c>
       <c r="Q4" t="n">
-        <v>205.8953960639884</v>
+        <v>206.4018389350628</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9994116346320761</v>
+        <v>0.9996255531647793</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6709134535602914</v>
+        <v>0.7078880786294662</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9982493302874232</v>
+        <v>0.9994671002910901</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9996408974427852</v>
+        <v>0.9996244895539534</v>
       </c>
       <c r="F5" t="n">
-        <v>0.999430743340603</v>
+        <v>0.9996053703298161</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003492790984601798</v>
+        <v>0.0002222878166480544</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1953599897652123</v>
+        <v>0.1734102551035131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001084733009394347</v>
+        <v>0.0001845970972997764</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000421310077907294</v>
+        <v>0.0002509325292717777</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0007530225018010701</v>
+        <v>0.0002177652092626634</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0112162278928343</v>
+        <v>0.009057395092640889</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01868901009845572</v>
+        <v>0.01490931979159527</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000403450538005</v>
+        <v>1.000256763544151</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01948463994993124</v>
+        <v>0.01554404040167018</v>
       </c>
       <c r="P5" t="n">
-        <v>133.9192784926076</v>
+        <v>134.8230750887954</v>
       </c>
       <c r="Q5" t="n">
-        <v>205.8329521598314</v>
+        <v>206.7367487560193</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9993890244579665</v>
+        <v>0.9996778189712897</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6700491860607826</v>
+        <v>0.707113944686361</v>
       </c>
       <c r="D6" t="n">
-        <v>0.997993480911487</v>
+        <v>0.9993655374752471</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9995946441350662</v>
+        <v>0.9996890269626675</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9993503124287217</v>
+        <v>0.9996125709656142</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003627014745202174</v>
+        <v>0.0001912605761382231</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1958730562873328</v>
+        <v>0.1738698144529855</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001243259921419607</v>
+        <v>0.0002197785783265937</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004755758699130471</v>
+        <v>0.0002078058057098428</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008594178956663275</v>
+        <v>0.0002137917422887739</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01146424454090381</v>
+        <v>0.008335059433578295</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01904472300980556</v>
+        <v>0.0138296990617375</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000418954657394</v>
+        <v>1.000220924133973</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01985549629634448</v>
+        <v>0.01441845798221936</v>
       </c>
       <c r="P6" t="n">
-        <v>133.8438608925694</v>
+        <v>135.123747573435</v>
       </c>
       <c r="Q6" t="n">
-        <v>205.7575345597932</v>
+        <v>207.0374212406588</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +792,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9993638930770845</v>
+        <v>0.9997178581215206</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6692411519326302</v>
+        <v>0.7062350126146708</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9977537367024553</v>
+        <v>0.9992714375353768</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9995528594690776</v>
+        <v>0.9997366185103862</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9992756342988645</v>
+        <v>0.9996118531888789</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003776205478308994</v>
+        <v>0.0001674916069599335</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1963527402510609</v>
+        <v>0.1743915864986293</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001391807905930687</v>
+        <v>0.0002523749101798435</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0005245989150829814</v>
+        <v>0.0001760030487779468</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009582034105068342</v>
+        <v>0.0002141878270557569</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0116664743759183</v>
+        <v>0.007665931931556572</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0194324611882</v>
+        <v>0.0129418548500566</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000436187604285</v>
+        <v>1.000193468716672</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02025974129172185</v>
+        <v>0.01349281640435631</v>
       </c>
       <c r="P7" t="n">
-        <v>133.7632414164968</v>
+        <v>135.3891546313129</v>
       </c>
       <c r="Q7" t="n">
-        <v>205.6769150837207</v>
+        <v>207.3028282985368</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +847,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9993376218385159</v>
+        <v>0.9997485258228586</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6684939908054812</v>
+        <v>0.7052852453030027</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9975311836707026</v>
+        <v>0.9991879158498107</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9995153471673902</v>
+        <v>0.9997706517372358</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9992068769791076</v>
+        <v>0.9996062437910632</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003932162899036328</v>
+        <v>0.0001492859346699462</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1967962873718166</v>
+        <v>0.174955409402647</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001529704059698939</v>
+        <v>0.000281306922074989</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0005686094920863337</v>
+        <v>0.0001532605557726261</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001049156775892636</v>
+        <v>0.0002172832144061875</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01183168618994926</v>
+        <v>0.007044569260520097</v>
       </c>
       <c r="M8" t="n">
-        <v>0.019829682042424</v>
+        <v>0.01221826234249151</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000454202167875</v>
+        <v>1.000172439435754</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02067387266007069</v>
+        <v>0.0127384190657012</v>
       </c>
       <c r="P8" t="n">
-        <v>133.6823014829929</v>
+        <v>135.6192941327275</v>
       </c>
       <c r="Q8" t="n">
-        <v>205.5959751502167</v>
+        <v>207.5329677999513</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9993111555125573</v>
+        <v>0.9997720066931088</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6678083621448511</v>
+        <v>0.7042974978768053</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9973259775660742</v>
+        <v>0.9991157945472035</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9994817472548185</v>
+        <v>0.9997940037248352</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9991439170813129</v>
+        <v>0.9995977454537903</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004089278442784255</v>
+        <v>0.0001353466757686566</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1972033061623827</v>
+        <v>0.175541778943305</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001656851878513922</v>
+        <v>0.0003062898276615134</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0006080299347950838</v>
+        <v>0.0001376557347255635</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001132441211775566</v>
+        <v>0.0002219727811935384</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0119671177916318</v>
+        <v>0.006489956494682278</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02022196440206602</v>
+        <v>0.01163385902306954</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000472350505675</v>
+        <v>1.000156338267582</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02108285529189911</v>
+        <v>0.01212913648708979</v>
       </c>
       <c r="P9" t="n">
-        <v>133.6039436746849</v>
+        <v>135.8153422049334</v>
       </c>
       <c r="Q9" t="n">
-        <v>205.5176173419087</v>
+        <v>207.7290158721572</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +957,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9992851565563179</v>
+        <v>0.9997899230031214</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6671828905454911</v>
+        <v>0.703300524627374</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9971378678030824</v>
+        <v>0.999054367821861</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9994516957496613</v>
+        <v>0.9998090977710514</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9990865351991015</v>
+        <v>0.9995876046885226</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0004243619477985901</v>
+        <v>0.0001247107802008671</v>
       </c>
       <c r="H10" t="n">
-        <v>0.197574613122729</v>
+        <v>0.1761336253311693</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001773406627728289</v>
+        <v>0.0003275681188770235</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0006432872776478076</v>
+        <v>0.0001275692318496393</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001208346952688048</v>
+        <v>0.0002275686753633314</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01207817207959895</v>
+        <v>0.005995364636592158</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02060004727661056</v>
+        <v>0.01116739809449216</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000490178361382</v>
+        <v>1.00014405279786</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02147703393715245</v>
+        <v>0.01164281735107563</v>
       </c>
       <c r="P10" t="n">
-        <v>133.5298476328326</v>
+        <v>135.9790265198601</v>
       </c>
       <c r="Q10" t="n">
-        <v>205.4435213000564</v>
+        <v>207.8927001870839</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1012,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9992600008402017</v>
+        <v>0.9998034979282324</v>
       </c>
       <c r="C11" t="n">
-        <v>0.666615972550435</v>
+        <v>0.7023168924428147</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9969659018091676</v>
+        <v>0.9990021660555304</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9994247825970688</v>
+        <v>0.999817917166009</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9990343257044816</v>
+        <v>0.999576560134937</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0004392954675555007</v>
+        <v>0.0001166521182487758</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1979111601341765</v>
+        <v>0.1767175518866216</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001879958531124288</v>
+        <v>0.0003456508732441996</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0006748626095067823</v>
+        <v>0.0001216757258056817</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001277410570315535</v>
+        <v>0.0002336632995249407</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01217004984989803</v>
+        <v>0.005539733201598927</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02095937660226326</v>
+        <v>0.0108005610154647</v>
       </c>
       <c r="N11" t="n">
-        <v>1.00050742799529</v>
+        <v>1.000134744277783</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02185166065611243</v>
+        <v>0.01126036325813653</v>
       </c>
       <c r="P11" t="n">
-        <v>133.4606766489202</v>
+        <v>136.112628801299</v>
       </c>
       <c r="Q11" t="n">
-        <v>205.374350316144</v>
+        <v>208.0263024685228</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1067,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9992359480813174</v>
+        <v>0.99981364460935</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6661029287673366</v>
+        <v>0.7013639581328543</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9968090127606429</v>
+        <v>0.9989574620542443</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9994006486835234</v>
+        <v>0.9998220024887717</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9989868791066832</v>
+        <v>0.9995650014366079</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0004535742242542793</v>
+        <v>0.0001106286100235452</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1982157250861613</v>
+        <v>0.1772832548576328</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001977168603660832</v>
+        <v>0.000361136392821562</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0007031772533091532</v>
+        <v>0.0001189457341781889</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001340173746092776</v>
+        <v>0.0002400416399048787</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01224646342244623</v>
+        <v>0.005121317105383251</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02129728208608505</v>
+        <v>0.01051801359685113</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000523921315668</v>
+        <v>1.000127786553589</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0222039514759413</v>
+        <v>0.01096578721095879</v>
       </c>
       <c r="P12" t="n">
-        <v>133.3967032640032</v>
+        <v>136.2186636443749</v>
       </c>
       <c r="Q12" t="n">
-        <v>205.310376931227</v>
+        <v>208.1323373115987</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1122,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9992132040353831</v>
+        <v>0.9998210936611056</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6656396762172325</v>
+        <v>0.7004538092012558</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9966662155165892</v>
+        <v>0.9989187795107967</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9993790983015336</v>
+        <v>0.9998225773774171</v>
       </c>
       <c r="F13" t="n">
-        <v>0.99894388014823</v>
+        <v>0.9995532134533242</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004670760724125431</v>
+        <v>0.0001062065311191283</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1984907318113711</v>
+        <v>0.1778235585798165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002065647248811823</v>
+        <v>0.0003745360721931552</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0007284608190555254</v>
+        <v>0.0001185615684023614</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001397053508032772</v>
+        <v>0.0002465465046946197</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01231036114287707</v>
+        <v>0.004738184631324601</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02161194281901891</v>
+        <v>0.01030565529789971</v>
       </c>
       <c r="N13" t="n">
-        <v>1.00053951723288</v>
+        <v>1.000122678632385</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02253200796771367</v>
+        <v>0.01074438837957873</v>
       </c>
       <c r="P13" t="n">
-        <v>133.3380368352063</v>
+        <v>136.300249905501</v>
       </c>
       <c r="Q13" t="n">
-        <v>205.2517105024301</v>
+        <v>208.2139235727248</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9991918174618319</v>
+        <v>0.9998264076768686</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6652227234560442</v>
+        <v>0.6995937920577329</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9965364266567057</v>
+        <v>0.9988849037628753</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9993597337831999</v>
+        <v>0.9998205743694627</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9989048950266506</v>
+        <v>0.9995413638569044</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000479772066324364</v>
+        <v>0.0001030519018087379</v>
       </c>
       <c r="H14" t="n">
-        <v>0.198738252981834</v>
+        <v>0.1783341019070178</v>
       </c>
       <c r="I14" t="n">
-        <v>0.002146065764969271</v>
+        <v>0.0003862706718384374</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0007511798628604442</v>
+        <v>0.0001199000660591971</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001448623697507192</v>
+        <v>0.0002530853689488173</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01236413530750836</v>
+        <v>0.004388444458240524</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0219036998318632</v>
+        <v>0.01015144826163922</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000554182311887</v>
+        <v>1.000119034735862</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02283618568061501</v>
+        <v>0.01058361643053206</v>
       </c>
       <c r="P14" t="n">
-        <v>133.2843988573383</v>
+        <v>136.3605555911889</v>
       </c>
       <c r="Q14" t="n">
-        <v>205.1980725245621</v>
+        <v>208.2742292584127</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1232,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9991717985943708</v>
+        <v>0.9998300384292937</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6648481275318422</v>
+        <v>0.6987889618526735</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9964183257419491</v>
+        <v>0.9988548279348555</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9993423827328417</v>
+        <v>0.9998167238288643</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9988695411684038</v>
+        <v>0.9995295939059267</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0004916561308193863</v>
+        <v>0.0001008965303288208</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1989606293041417</v>
+        <v>0.1788118838835956</v>
       </c>
       <c r="I15" t="n">
-        <v>0.002219242309782845</v>
+        <v>0.0003966889746795062</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0007715366445967911</v>
+        <v>0.0001224731659598429</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001495390389377945</v>
+        <v>0.0002595802831211331</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01241000889414439</v>
+        <v>0.004070065132726458</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02217332024797789</v>
+        <v>0.01004472649348009</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000567909535289</v>
+        <v>1.000116545077056</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0231172843960349</v>
+        <v>0.01047235129575788</v>
       </c>
       <c r="P15" t="n">
-        <v>133.23546201386</v>
+        <v>136.4028300368454</v>
       </c>
       <c r="Q15" t="n">
-        <v>205.1491356810838</v>
+        <v>208.3165037040693</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1287,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.999153220794187</v>
+        <v>0.9998323684163987</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6645102740749296</v>
+        <v>0.6980408566649918</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9963112559147727</v>
+        <v>0.9988280556521804</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9993268803111881</v>
+        <v>0.9998115631665137</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9988375913045973</v>
+        <v>0.9995180636742653</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0005026847155276188</v>
+        <v>9.951334933309927e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1991611937106744</v>
+        <v>0.1792559914394649</v>
       </c>
       <c r="I16" t="n">
-        <v>0.002285583878962977</v>
+        <v>0.00040596292545726</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0007897245587271532</v>
+        <v>0.0001259217466052107</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001537654218845065</v>
+        <v>0.000265942914976429</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01244876622644215</v>
+        <v>0.003780929005144634</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02242063147031365</v>
+        <v>0.009975637790793091</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000580648598272</v>
+        <v>1.000114947371612</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02337512416911031</v>
+        <v>0.01040032134396417</v>
       </c>
       <c r="P16" t="n">
-        <v>133.1910947849741</v>
+        <v>136.4304375172944</v>
       </c>
       <c r="Q16" t="n">
-        <v>205.1047684521979</v>
+        <v>208.3441111845182</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9991359704752089</v>
+        <v>0.9998336814540872</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6642072962632701</v>
+        <v>0.6973495949753103</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9962140169176525</v>
+        <v>0.9988039046592756</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9993129124836756</v>
+        <v>0.9998055454141147</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9988086229443114</v>
+        <v>0.9995068386594336</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0005129252500480406</v>
+        <v>9.873387344092856e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1993410544276355</v>
+        <v>0.17966635423941</v>
       </c>
       <c r="I17" t="n">
-        <v>0.002345834164450198</v>
+        <v>0.0004143288583196697</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0008061120401841114</v>
+        <v>0.000129943072365697</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001575974064165113</v>
+        <v>0.0002721371215668478</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01249923397985436</v>
+        <v>0.003723526687994121</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02264785310019563</v>
+        <v>0.009936492008799109</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000592477388428</v>
+        <v>1.000114047002912</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02361201909418997</v>
+        <v>0.01035950904498776</v>
       </c>
       <c r="P17" t="n">
-        <v>133.1507608696355</v>
+        <v>136.4461649488927</v>
       </c>
       <c r="Q17" t="n">
-        <v>205.0644345368594</v>
+        <v>208.3598386161166</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9991200874218653</v>
+        <v>0.9998342310612601</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6639348396225182</v>
+        <v>0.6967138385254721</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9961260518163881</v>
+        <v>0.9987822098911996</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9993004210984793</v>
+        <v>0.9997989857360498</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9987824827359701</v>
+        <v>0.9994960616847653</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005223541166249632</v>
+        <v>9.840760288130641e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1995027964590999</v>
+        <v>0.1800437667312826</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002400338248419139</v>
+        <v>0.0004218439519601193</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0008207673144630045</v>
+        <v>0.0001343265365951624</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001610552781441072</v>
+        <v>0.0002780840898795713</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0125583881639459</v>
+        <v>0.00372707609574319</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02285506763553683</v>
+        <v>0.009920060628912829</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000603368625007</v>
+        <v>1.000113670129422</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02382805518129388</v>
+        <v>0.01034237814724208</v>
       </c>
       <c r="P18" t="n">
-        <v>133.1143296314825</v>
+        <v>136.4527849836739</v>
       </c>
       <c r="Q18" t="n">
-        <v>205.0280032987064</v>
+        <v>208.3664586508977</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9991054557604607</v>
+        <v>0.9998342043305533</v>
       </c>
       <c r="C19" t="n">
-        <v>0.663690236009606</v>
+        <v>0.6961313308869603</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9960463218207761</v>
+        <v>0.9987625601453712</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9992891926327002</v>
+        <v>0.9997921721827291</v>
       </c>
       <c r="F19" t="n">
-        <v>0.998758830728102</v>
+        <v>0.9994857680612966</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005310401028895649</v>
+        <v>9.842347138358149e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1996480037300504</v>
+        <v>0.180389568428523</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002449739775993378</v>
+        <v>0.0004286506474450994</v>
       </c>
       <c r="J19" t="n">
-        <v>0.000833940893144297</v>
+        <v>0.0001388796513915324</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001641840064327453</v>
+        <v>0.000283764334519266</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01261104134332974</v>
+        <v>0.003730025551117178</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02304430738576373</v>
+        <v>0.009920860415487232</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000613401764255</v>
+        <v>1.000113688459049</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02402535125946823</v>
+        <v>0.01034321198238674</v>
       </c>
       <c r="P19" t="n">
-        <v>133.0813460324831</v>
+        <v>136.4524625040579</v>
       </c>
       <c r="Q19" t="n">
-        <v>204.995019699707</v>
+        <v>208.3661361712817</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9990920294797827</v>
+        <v>0.9998337573175853</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6634701659352586</v>
+        <v>0.6955991497684917</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9959741433490271</v>
+        <v>0.9987448197996982</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9992791301854076</v>
+        <v>0.9997852615684155</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9987374647389931</v>
+        <v>0.9994760126248955</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0005390105230851613</v>
+        <v>9.868883759134565e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1997786468327152</v>
+        <v>0.1807054941294733</v>
       </c>
       <c r="I20" t="n">
-        <v>0.00249446230149966</v>
+        <v>0.0004347959244298254</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0008457464633571612</v>
+        <v>0.0001434976265951283</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001670103362273315</v>
+        <v>0.0002891475958649423</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01265791985268105</v>
+        <v>0.003732665900145205</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02321660016206424</v>
+        <v>0.009934225565757284</v>
       </c>
       <c r="N20" t="n">
-        <v>1.00062260835672</v>
+        <v>1.000113994982227</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02420497889595106</v>
+        <v>0.01035714611477346</v>
       </c>
       <c r="P20" t="n">
-        <v>133.0515509277935</v>
+        <v>136.4470774244662</v>
       </c>
       <c r="Q20" t="n">
-        <v>204.9652245950174</v>
+        <v>208.36075109169</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9990797346093871</v>
+        <v>0.9998330036018106</v>
       </c>
       <c r="C21" t="n">
-        <v>0.663272581436233</v>
+        <v>0.6951140127738438</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9959088626238358</v>
+        <v>0.9987287180891496</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9992700895567357</v>
+        <v>0.9997784165572144</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9987181658107501</v>
+        <v>0.9994668162677772</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000546309289262758</v>
+        <v>9.91362758339823e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1998959415265428</v>
+        <v>0.1809934924063233</v>
       </c>
       <c r="I21" t="n">
-        <v>0.002534910912099076</v>
+        <v>0.0004403735762452482</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0008563532047839538</v>
+        <v>0.0001480717629251978</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00169563231654683</v>
+        <v>0.0002942223451390513</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01269970923701268</v>
+        <v>0.003734907857305373</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02337326013338229</v>
+        <v>0.009956720134360627</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000631039124992</v>
+        <v>1.000114511815901</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02436830820657897</v>
+        <v>0.01038059832373242</v>
       </c>
       <c r="P21" t="n">
-        <v>133.0246505574965</v>
+        <v>136.4380302615883</v>
       </c>
       <c r="Q21" t="n">
-        <v>204.9383242247203</v>
+        <v>208.3517039288122</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9990684907258959</v>
+        <v>0.9998320452822927</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6630951462990341</v>
+        <v>0.6946729918424567</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9958497992827934</v>
+        <v>0.9987141655691025</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9992619722637546</v>
+        <v>0.9997717352522786</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9987007336233047</v>
+        <v>0.9994582015749676</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0005529841442136082</v>
+        <v>9.970517569707779e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2000012746887829</v>
+        <v>0.1812553014823068</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002571507167357069</v>
+        <v>0.0004454145866158202</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0008658766606034245</v>
+        <v>0.0001525365035576284</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001718691913980247</v>
+        <v>0.0002989761194347064</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01273708474252386</v>
+        <v>0.003736886254544197</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02351561490188186</v>
+        <v>0.009985247903636533</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000638749216529</v>
+        <v>1.000115168949285</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02451672331228856</v>
+        <v>0.01041034057920703</v>
       </c>
       <c r="P22" t="n">
-        <v>133.0003624583222</v>
+        <v>136.42658593927</v>
       </c>
       <c r="Q22" t="n">
-        <v>204.9140361255461</v>
+        <v>208.3402596064938</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.999058239510309</v>
+        <v>0.9998309555669412</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6629355829476997</v>
+        <v>0.6942722591000454</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9957964437645417</v>
+        <v>0.9987009950711828</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9992546910763537</v>
+        <v>0.9997653108410182</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9986850089849774</v>
+        <v>0.9994501767941385</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0005590697086154433</v>
+        <v>0.0001003520778029435</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2000959983869128</v>
+        <v>0.1814931937489553</v>
       </c>
       <c r="I23" t="n">
-        <v>0.002604566796746421</v>
+        <v>0.000449976862866523</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0008744191718429033</v>
+        <v>0.0001568295765830295</v>
       </c>
       <c r="K23" t="n">
-        <v>0.001739492736065892</v>
+        <v>0.000303404367507693</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01277034858475127</v>
+        <v>0.003738611764813553</v>
       </c>
       <c r="M23" t="n">
-        <v>0.02364465496926194</v>
+        <v>0.01001758842251684</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000645778621502</v>
+        <v>1.000115916182669</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02465125688248677</v>
+        <v>0.01044405790093018</v>
       </c>
       <c r="P23" t="n">
-        <v>132.9784727804613</v>
+        <v>136.4136515547526</v>
       </c>
       <c r="Q23" t="n">
-        <v>204.8921464476851</v>
+        <v>208.3273252219765</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9990488879254299</v>
+        <v>0.9998297789217271</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6627924410778449</v>
+        <v>0.6939089741170792</v>
       </c>
       <c r="D24" t="n">
-        <v>0.995748214801667</v>
+        <v>0.9986890229357963</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9992481249201067</v>
+        <v>0.9997591636439451</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9986708018873914</v>
+        <v>0.9994427006316179</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0005646212133671224</v>
+        <v>0.0001010505852305237</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2001809735842655</v>
+        <v>0.1817088554079382</v>
       </c>
       <c r="I24" t="n">
-        <v>0.002634449959551583</v>
+        <v>0.0004541240249007369</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0008821227867138023</v>
+        <v>0.0001609374029449704</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001758286129152967</v>
+        <v>0.000307529876101695</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01280017083924697</v>
+        <v>0.003740177181712999</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02376175947540759</v>
+        <v>0.0100523920153625</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000652191136848</v>
+        <v>1.000116723025101</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02477334676989879</v>
+        <v>0.01048034315477664</v>
       </c>
       <c r="P24" t="n">
-        <v>132.9587109409366</v>
+        <v>136.3997786452737</v>
       </c>
       <c r="Q24" t="n">
-        <v>204.8723846081604</v>
+        <v>208.3134523124976</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9990403807618942</v>
+        <v>0.999828577801514</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6626635624765358</v>
+        <v>0.6935799275466514</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9957046488013753</v>
+        <v>0.9986782208557327</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9992422378264835</v>
+        <v>0.9997533827408946</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9986579871766886</v>
+        <v>0.9994358073466379</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0005696714331322713</v>
+        <v>0.0001017636220746679</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2002574814892683</v>
+        <v>0.1819041916662158</v>
       </c>
       <c r="I25" t="n">
-        <v>0.002661443902648999</v>
+        <v>0.0004578658783699817</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0008890297045934334</v>
+        <v>0.000164800455595639</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001775237648918184</v>
+        <v>0.0003113337402294512</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01282693082071996</v>
+        <v>0.003741554897240029</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0238677907048866</v>
+        <v>0.01008779569949094</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000658024620416</v>
+        <v>1.00011754665039</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02488389196833163</v>
+        <v>0.01051725404703416</v>
       </c>
       <c r="P25" t="n">
-        <v>132.9409015928768</v>
+        <v>136.3857157294374</v>
       </c>
       <c r="Q25" t="n">
-        <v>204.8545752601006</v>
+        <v>208.2993893966612</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9990326524514352</v>
+        <v>0.999827370404177</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6625477411918959</v>
+        <v>0.6932820664885819</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9956653011507258</v>
+        <v>0.9986684719440158</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9992369624108383</v>
+        <v>0.9997479223623991</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9986464347799554</v>
+        <v>0.9994294407601143</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0005742592920662805</v>
+        <v>0.0001024803852907858</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2003262380070495</v>
+        <v>0.1820810148572136</v>
       </c>
       <c r="I26" t="n">
-        <v>0.002685824112802266</v>
+        <v>0.0004612429130628032</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0008952189832043422</v>
+        <v>0.0001684493196980855</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001790519358049261</v>
+        <v>0.000314846960727938</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01285082274872389</v>
+        <v>0.003742798616058596</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02396370781131919</v>
+        <v>0.01012325961786942</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000663324033302</v>
+        <v>1.000118374579993</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02498389246456083</v>
+        <v>0.01055422773783845</v>
       </c>
       <c r="P26" t="n">
-        <v>132.9248590706095</v>
+        <v>136.3716782814296</v>
       </c>
       <c r="Q26" t="n">
-        <v>204.8385327378334</v>
+        <v>208.2853519486534</v>
       </c>
     </row>
   </sheetData>
